--- a/resources/templates/08调查了解记录基本情况表.xlsx
+++ b/resources/templates/08调查了解记录基本情况表.xlsx
@@ -1577,7 +1577,11 @@
         </is>
       </c>
       <c r="B6" s="33" t="n"/>
-      <c r="C6" s="7" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>{unitNature}</t>
+        </is>
+      </c>
       <c r="D6" s="34" t="n"/>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="7" t="inlineStr">
@@ -1586,26 +1590,42 @@
 代表</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>{legalRepresentative}</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
           <t>主管单位</t>
         </is>
       </c>
       <c r="I6" s="33" t="n"/>
-      <c r="J6" s="7" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>{supervisingUnit}</t>
+        </is>
+      </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
           <t>人员编制</t>
         </is>
       </c>
-      <c r="L6" s="7" t="n"/>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>{staffQuota}</t>
+        </is>
+      </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
           <t>期末人数</t>
         </is>
       </c>
-      <c r="N6" s="9" t="n"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>{currentStaffCount}</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="1">
       <c r="A7" s="35" t="n"/>
@@ -1630,7 +1650,11 @@
         </is>
       </c>
       <c r="B8" s="14" t="n"/>
-      <c r="C8" s="15" t="n"/>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>{orgStructure}</t>
+        </is>
+      </c>
       <c r="D8" s="41" t="n"/>
       <c r="E8" s="41" t="n"/>
       <c r="F8" s="41" t="n"/>
@@ -1649,7 +1673,11 @@
           <t>职责范围或经营范围、业务活动及其目标</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>{responsibilityScope}</t>
+        </is>
+      </c>
       <c r="C9" s="43" t="n"/>
       <c r="D9" s="43" t="n"/>
       <c r="E9" s="43" t="n"/>
@@ -1685,7 +1713,11 @@
           <t>相关法律法规、政策及其执行情况</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>{lawExecution}</t>
+        </is>
+      </c>
       <c r="C11" s="41" t="n"/>
       <c r="D11" s="41" t="n"/>
       <c r="E11" s="41" t="n"/>
@@ -1705,7 +1737,11 @@
           <t>财政财务管理体制和业务管理体制</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>{financialSystem}</t>
+        </is>
+      </c>
       <c r="C12" s="41" t="n"/>
       <c r="D12" s="41" t="n"/>
       <c r="E12" s="41" t="n"/>
@@ -1725,7 +1761,11 @@
           <t>适用的业绩指标体系以及业绩评价情况</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n"/>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>{performanceIndicators}</t>
+        </is>
+      </c>
       <c r="C13" s="43" t="n"/>
       <c r="D13" s="43" t="n"/>
       <c r="E13" s="43" t="n"/>
@@ -1786,7 +1826,11 @@
           <t>相关内部控制及其执行情况</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n"/>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>{internalControl}</t>
+        </is>
+      </c>
       <c r="C20" s="43" t="n"/>
       <c r="D20" s="43" t="n"/>
       <c r="E20" s="43" t="n"/>
@@ -1847,7 +1891,11 @@
           <t>相关信息系统及其电子数据情况</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n"/>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>{infoSystems}</t>
+        </is>
+      </c>
       <c r="C27" s="43" t="n"/>
       <c r="D27" s="43" t="n"/>
       <c r="E27" s="43" t="n"/>
@@ -1883,7 +1931,11 @@
           <t>经济环境、行业状况及其他外部因素</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n"/>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>{economicEnvironment}</t>
+        </is>
+      </c>
       <c r="C29" s="43" t="n"/>
       <c r="D29" s="43" t="n"/>
       <c r="E29" s="43" t="n"/>
@@ -1925,7 +1977,11 @@
 审计情况</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n"/>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>{previousAudit}</t>
+        </is>
+      </c>
       <c r="C32" s="43" t="n"/>
       <c r="D32" s="43" t="n"/>
       <c r="E32" s="43" t="n"/>
@@ -1973,7 +2029,11 @@
         </is>
       </c>
       <c r="B36" s="29" t="n"/>
-      <c r="C36" s="30" t="n"/>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>{otherInfo}</t>
+        </is>
+      </c>
       <c r="D36" s="49" t="n"/>
       <c r="E36" s="49" t="n"/>
       <c r="F36" s="49" t="n"/>
@@ -1989,7 +2049,7 @@
     <row r="37" ht="22.5" customHeight="1" s="1">
       <c r="A37" s="32" t="inlineStr">
         <is>
-          <t>填表人：                                               年  月 日</t>
+          <t>填表人：{fillerName}                    {fillDate}</t>
         </is>
       </c>
     </row>
